--- a/data/trans_dic/P35-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P35-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 25,04</t>
+          <t>16,04; 25,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 30,41</t>
+          <t>19,23; 29,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,88; 40,94</t>
+          <t>29,08; 40,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 17,1</t>
+          <t>9,2; 16,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 28,99</t>
+          <t>18,11; 28,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,24; 46,59</t>
+          <t>33,98; 46,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,05; 49,44</t>
+          <t>38,54; 50,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,45</t>
+          <t>9,04; 14,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,34</t>
+          <t>18,24; 25,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,89; 35,73</t>
+          <t>27,64; 35,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,29; 43,42</t>
+          <t>35,26; 43,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,5</t>
+          <t>9,8; 14,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,12; 27,32</t>
+          <t>19,51; 27,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,0; 42,24</t>
+          <t>33,07; 42,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,09; 31,88</t>
+          <t>24,13; 31,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,33; 44,95</t>
+          <t>33,44; 44,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 36,95</t>
+          <t>28,66; 36,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,87; 49,21</t>
+          <t>40,04; 49,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,98; 40,68</t>
+          <t>31,98; 40,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,24; 44,94</t>
+          <t>36,97; 44,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,31; 31,26</t>
+          <t>25,32; 31,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,86; 44,44</t>
+          <t>37,72; 44,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 35,08</t>
+          <t>29,22; 35,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,46; 43,42</t>
+          <t>36,66; 43,27</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 18,06</t>
+          <t>10,12; 17,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 28,63</t>
+          <t>19,01; 28,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,81; 31,46</t>
+          <t>21,92; 31,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 32,2</t>
+          <t>23,11; 32,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,86</t>
+          <t>14,82; 23,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,21; 34,8</t>
+          <t>24,68; 34,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,19; 38,62</t>
+          <t>28,2; 38,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,04; 33,29</t>
+          <t>24,73; 32,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,17</t>
+          <t>13,17; 19,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,75; 29,75</t>
+          <t>22,91; 29,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 33,81</t>
+          <t>26,37; 33,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,63</t>
+          <t>25,52; 31,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 22,14</t>
+          <t>14,21; 21,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 21,0</t>
+          <t>12,53; 20,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 35,56</t>
+          <t>25,85; 35,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 26,75</t>
+          <t>16,71; 26,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 28,75</t>
+          <t>19,66; 28,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 37,34</t>
+          <t>27,44; 37,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,53; 43,14</t>
+          <t>32,61; 42,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 24,99</t>
+          <t>12,22; 25,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 24,2</t>
+          <t>17,9; 23,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,1; 27,79</t>
+          <t>21,31; 28,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,63; 37,74</t>
+          <t>30,71; 37,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 24,38</t>
+          <t>14,55; 24,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 14,16</t>
+          <t>5,76; 14,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,01; 29,1</t>
+          <t>16,71; 28,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,09; 47,24</t>
+          <t>33,67; 46,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,71; 36,1</t>
+          <t>23,95; 35,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 18,74</t>
+          <t>9,23; 19,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,01; 42,42</t>
+          <t>29,87; 42,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,08; 56,82</t>
+          <t>43,81; 56,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 34,71</t>
+          <t>25,71; 34,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 15,21</t>
+          <t>8,59; 15,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 33,49</t>
+          <t>24,68; 34,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,05; 50,26</t>
+          <t>40,32; 49,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,23; 33,76</t>
+          <t>26,81; 34,03</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 26,86</t>
+          <t>16,36; 26,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,6; 35,12</t>
+          <t>23,71; 35,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 28,0</t>
+          <t>17,41; 27,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,61; 35,42</t>
+          <t>25,77; 35,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 29,26</t>
+          <t>18,8; 29,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,17; 44,37</t>
+          <t>32,29; 44,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 37,14</t>
+          <t>26,32; 37,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,17; 34,11</t>
+          <t>26,27; 34,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,76; 25,92</t>
+          <t>18,98; 26,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,26</t>
+          <t>29,35; 37,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,58; 31,39</t>
+          <t>23,55; 31,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,89; 33,37</t>
+          <t>27,02; 33,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 16,03</t>
+          <t>10,61; 15,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,98; 30,19</t>
+          <t>23,01; 30,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,67; 34,5</t>
+          <t>26,58; 34,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,19; 27,16</t>
+          <t>20,35; 27,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,98</t>
+          <t>11,16; 17,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,62; 37,11</t>
+          <t>29,87; 37,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,67; 39,2</t>
+          <t>31,88; 39,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 34,38</t>
+          <t>13,13; 34,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 15,48</t>
+          <t>11,69; 15,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,54; 32,61</t>
+          <t>27,23; 32,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,43; 35,73</t>
+          <t>30,16; 35,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,44; 29,27</t>
+          <t>16,4; 29,38</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,36; 22,11</t>
+          <t>16,3; 22,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,26; 27,83</t>
+          <t>21,09; 28,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 24,03</t>
+          <t>18,15; 23,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,08; 62,02</t>
+          <t>20,1; 61,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,55; 24,71</t>
+          <t>18,51; 24,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,51; 31,3</t>
+          <t>24,79; 31,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,18; 29,79</t>
+          <t>23,34; 29,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,29; 68,71</t>
+          <t>62,93; 68,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,23; 22,32</t>
+          <t>17,98; 22,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,92; 28,86</t>
+          <t>23,77; 28,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,67; 26,07</t>
+          <t>21,63; 26,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,88; 64,03</t>
+          <t>32,99; 64,18</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,12; 18,85</t>
+          <t>16,32; 18,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,59</t>
+          <t>24,28; 27,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,19; 29,48</t>
+          <t>26,3; 29,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,92; 34,82</t>
+          <t>24,37; 34,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,04; 22,99</t>
+          <t>20,12; 22,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,02</t>
+          <t>32,68; 36,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,12; 36,65</t>
+          <t>32,85; 36,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,54; 37,25</t>
+          <t>27,51; 37,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,59</t>
+          <t>18,61; 20,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,16; 31,54</t>
+          <t>29,24; 31,39</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,3; 32,64</t>
+          <t>30,31; 32,56</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,57; 35,27</t>
+          <t>28,79; 35,56</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40371; 65276</t>
+          <t>41809; 67134</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53666; 85832</t>
+          <t>54281; 83776</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83686; 118640</t>
+          <t>84268; 117139</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29830; 53249</t>
+          <t>28642; 52123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45668; 74342</t>
+          <t>46439; 74063</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96809; 131738</t>
+          <t>96074; 131263</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>109838; 142728</t>
+          <t>111271; 145105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25499; 41856</t>
+          <t>26175; 42294</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92626; 131053</t>
+          <t>94337; 132967</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157597; 201903</t>
+          <t>156184; 203166</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>204145; 251189</t>
+          <t>203994; 251577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57362; 87137</t>
+          <t>58913; 87509</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88936; 127116</t>
+          <t>90777; 126675</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164394; 210424</t>
+          <t>164752; 211973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121091; 160210</t>
+          <t>121249; 160755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172766; 233022</t>
+          <t>173365; 231232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136427; 176178</t>
+          <t>136651; 175874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>205180; 253261</t>
+          <t>206041; 254393</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165950; 211106</t>
+          <t>165951; 211247</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>191507; 231088</t>
+          <t>190129; 229957</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>238417; 294498</t>
+          <t>238486; 294119</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>383424; 450040</t>
+          <t>381999; 448903</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>298190; 358334</t>
+          <t>298512; 358590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>376476; 448375</t>
+          <t>378536; 446845</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31546; 55560</t>
+          <t>31146; 55034</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60863; 91232</t>
+          <t>60601; 91259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67992; 98087</t>
+          <t>68354; 98608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73909; 101771</t>
+          <t>73036; 102989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47726; 74456</t>
+          <t>48258; 75711</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81343; 116954</t>
+          <t>82933; 117217</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94231; 129101</t>
+          <t>94276; 128327</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87306; 116084</t>
+          <t>86235; 114545</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85991; 121396</t>
+          <t>83419; 121077</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148954; 194817</t>
+          <t>150001; 195941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171681; 218410</t>
+          <t>170378; 215147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167952; 210259</t>
+          <t>169678; 209803</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47991; 75757</t>
+          <t>48617; 74286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43758; 75178</t>
+          <t>44849; 74956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94272; 130520</t>
+          <t>94896; 129050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53314; 83600</t>
+          <t>52243; 84113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67778; 99648</t>
+          <t>68146; 98390</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99989; 135739</t>
+          <t>99730; 136878</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124401; 164989</t>
+          <t>124711; 162448</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54446; 118859</t>
+          <t>58138; 122466</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124205; 166691</t>
+          <t>123285; 165050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152220; 200515</t>
+          <t>153785; 202315</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229553; 282873</t>
+          <t>230192; 284227</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120209; 192146</t>
+          <t>114659; 191433</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11569; 27187</t>
+          <t>11058; 27620</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35647; 60977</t>
+          <t>35020; 60213</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71490; 99063</t>
+          <t>70609; 98463</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44170; 64531</t>
+          <t>42810; 63687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17373; 37072</t>
+          <t>18269; 37671</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63451; 92778</t>
+          <t>65323; 93160</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96359; 124197</t>
+          <t>95754; 124230</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53722; 72021</t>
+          <t>53347; 71173</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32519; 59282</t>
+          <t>33470; 58778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108183; 143409</t>
+          <t>105691; 145658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>175812; 215246</t>
+          <t>172695; 213681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>101291; 130402</t>
+          <t>103559; 131425</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41914; 67906</t>
+          <t>41356; 66825</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63990; 95231</t>
+          <t>64284; 95594</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45311; 72651</t>
+          <t>45172; 72493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69046; 95510</t>
+          <t>69497; 94720</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48140; 74968</t>
+          <t>48158; 74539</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88909; 122617</t>
+          <t>89222; 121925</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70918; 100311</t>
+          <t>71110; 100599</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67281; 87680</t>
+          <t>67528; 88775</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95498; 131916</t>
+          <t>96612; 133973</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>162457; 209479</t>
+          <t>160696; 207108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124875; 166252</t>
+          <t>124697; 164937</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>141607; 175736</t>
+          <t>142330; 175677</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>63300; 95117</t>
+          <t>62933; 94224</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>149304; 196079</t>
+          <t>149483; 195095</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170415; 220440</t>
+          <t>169838; 218577</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126063; 169568</t>
+          <t>127071; 171380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68634; 103021</t>
+          <t>67678; 104408</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>201938; 252969</t>
+          <t>203601; 253132</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>214010; 264910</t>
+          <t>215431; 265678</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>105063; 291678</t>
+          <t>111420; 292034</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>139411; 185770</t>
+          <t>140299; 186685</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>366644; 434140</t>
+          <t>362482; 434938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>400137; 469789</t>
+          <t>396506; 465584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>227444; 431087</t>
+          <t>241565; 432663</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116699; 157738</t>
+          <t>116228; 158388</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>157325; 206021</t>
+          <t>156095; 207730</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>137567; 182695</t>
+          <t>137966; 181556</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>177241; 575996</t>
+          <t>186647; 571656</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>137604; 183332</t>
+          <t>137285; 183661</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>190789; 243695</t>
+          <t>193007; 245289</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>187092; 240426</t>
+          <t>188334; 239761</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>445258; 491191</t>
+          <t>449839; 492062</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>265272; 324811</t>
+          <t>261631; 324510</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>363304; 438288</t>
+          <t>361009; 435679</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>339647; 408644</t>
+          <t>338937; 408873</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>556795; 1052390</t>
+          <t>542223; 1054883</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>504055; 589433</t>
+          <t>510422; 590682</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>808315; 918082</t>
+          <t>808044; 923851</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>874749; 984567</t>
+          <t>878132; 981053</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>862249; 1204823</t>
+          <t>843324; 1198696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>643049; 737446</t>
+          <t>645355; 734471</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1128156; 1243553</t>
+          <t>1128096; 1245567</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1157730; 1281273</t>
+          <t>1148481; 1268184</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1043356; 1361965</t>
+          <t>1005768; 1371118</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1182969; 1304283</t>
+          <t>1178787; 1297968</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1976645; 2138551</t>
+          <t>1982308; 2128182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2070915; 2231270</t>
+          <t>2071546; 2225499</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2032995; 2509442</t>
+          <t>2048831; 2530350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P35-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P35-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 25,75</t>
+          <t>15,65; 25,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 29,68</t>
+          <t>19,33; 29,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,08; 40,42</t>
+          <t>29,12; 40,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,74</t>
+          <t>9,5; 16,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 28,88</t>
+          <t>18,18; 28,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 46,42</t>
+          <t>34,02; 46,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,54; 50,26</t>
+          <t>38,53; 50,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,6</t>
+          <t>8,39; 13,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 25,71</t>
+          <t>18,23; 25,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,64; 35,96</t>
+          <t>28,3; 36,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,26; 43,49</t>
+          <t>35,64; 43,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,56</t>
+          <t>9,87; 14,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,51; 27,23</t>
+          <t>19,16; 27,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,07; 42,55</t>
+          <t>33,32; 42,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,13; 31,99</t>
+          <t>24,08; 32,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 44,61</t>
+          <t>33,94; 44,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 36,89</t>
+          <t>28,66; 37,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,04; 49,43</t>
+          <t>39,59; 48,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,98; 40,71</t>
+          <t>31,54; 40,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,97; 44,72</t>
+          <t>37,38; 45,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 31,22</t>
+          <t>24,94; 31,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 44,32</t>
+          <t>37,88; 44,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 35,1</t>
+          <t>29,37; 35,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 43,27</t>
+          <t>37,09; 43,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 17,89</t>
+          <t>9,84; 17,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 28,63</t>
+          <t>19,37; 28,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,92; 31,63</t>
+          <t>22,17; 31,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 32,59</t>
+          <t>23,52; 33,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 23,25</t>
+          <t>14,88; 23,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,68; 34,88</t>
+          <t>24,35; 34,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,2; 38,39</t>
+          <t>27,82; 38,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 32,85</t>
+          <t>25,57; 33,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 19,12</t>
+          <t>13,41; 19,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,91; 29,93</t>
+          <t>23,04; 29,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,3</t>
+          <t>26,3; 33,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,52; 31,56</t>
+          <t>25,78; 31,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 21,71</t>
+          <t>14,17; 22,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 20,94</t>
+          <t>12,4; 20,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,85; 35,16</t>
+          <t>25,89; 35,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 26,91</t>
+          <t>17,61; 28,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 28,39</t>
+          <t>20,35; 29,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 37,66</t>
+          <t>27,69; 37,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,61; 42,48</t>
+          <t>32,26; 42,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 25,74</t>
+          <t>20,78; 29,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 23,96</t>
+          <t>18,21; 24,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 28,04</t>
+          <t>21,13; 27,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 37,92</t>
+          <t>30,64; 38,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 24,29</t>
+          <t>20,66; 27,06</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,38</t>
+          <t>5,53; 13,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,71; 28,74</t>
+          <t>16,76; 28,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,67; 46,95</t>
+          <t>34,15; 46,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 35,63</t>
+          <t>24,82; 35,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 19,04</t>
+          <t>9,06; 19,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 42,6</t>
+          <t>29,46; 42,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,81; 56,83</t>
+          <t>43,24; 56,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,71; 34,31</t>
+          <t>25,83; 35,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 15,08</t>
+          <t>8,57; 15,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,68; 34,01</t>
+          <t>24,88; 33,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,32; 49,89</t>
+          <t>40,77; 50,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,81; 34,03</t>
+          <t>26,07; 33,4</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,36; 26,43</t>
+          <t>16,46; 26,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,71; 35,26</t>
+          <t>23,99; 35,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,41; 27,94</t>
+          <t>17,22; 28,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,77; 35,13</t>
+          <t>25,0; 34,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 29,09</t>
+          <t>18,83; 29,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,29; 44,12</t>
+          <t>32,98; 44,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,32; 37,24</t>
+          <t>25,39; 37,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,27; 34,54</t>
+          <t>26,38; 34,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 26,32</t>
+          <t>18,17; 25,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,35; 37,83</t>
+          <t>29,82; 37,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,55; 31,14</t>
+          <t>23,11; 30,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,02; 33,35</t>
+          <t>26,8; 32,93</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 15,88</t>
+          <t>10,42; 15,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,01; 30,03</t>
+          <t>22,83; 30,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,58; 34,21</t>
+          <t>26,36; 34,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,35; 27,45</t>
+          <t>21,1; 27,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,21</t>
+          <t>11,36; 16,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,87; 37,13</t>
+          <t>29,58; 37,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,88; 39,32</t>
+          <t>31,51; 39,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,13; 34,42</t>
+          <t>30,51; 36,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 15,56</t>
+          <t>11,84; 15,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,23; 32,67</t>
+          <t>27,56; 32,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,16; 35,41</t>
+          <t>30,38; 35,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 29,38</t>
+          <t>26,87; 31,45</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,3; 22,21</t>
+          <t>16,46; 22,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,09; 28,07</t>
+          <t>21,07; 27,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,15; 23,88</t>
+          <t>18,15; 24,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,1; 61,55</t>
+          <t>56,05; 63,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 24,76</t>
+          <t>18,35; 24,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,79; 31,51</t>
+          <t>24,88; 31,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,34; 29,71</t>
+          <t>22,93; 29,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,93; 68,83</t>
+          <t>61,19; 67,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,98; 22,3</t>
+          <t>18,14; 22,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,77; 28,69</t>
+          <t>23,87; 28,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,63; 26,09</t>
+          <t>21,49; 25,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,99; 64,18</t>
+          <t>59,83; 64,75</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,28; 18,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,76</t>
+          <t>24,29; 27,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,3; 29,38</t>
+          <t>26,35; 29,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,37; 34,65</t>
+          <t>32,68; 36,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,89</t>
+          <t>20,18; 23,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,08</t>
+          <t>32,8; 36,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,28</t>
+          <t>33,29; 36,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,51; 37,5</t>
+          <t>36,56; 39,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,61; 20,49</t>
+          <t>18,61; 20,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,24; 31,39</t>
+          <t>29,17; 31,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,31; 32,56</t>
+          <t>30,37; 32,66</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,79; 35,56</t>
+          <t>35,18; 37,41</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71618</t>
+          <t>74861</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41809; 67134</t>
+          <t>40794; 66239</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54281; 83776</t>
+          <t>54548; 84335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84268; 117139</t>
+          <t>84379; 117045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28642; 52123</t>
+          <t>30299; 52588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46439; 74063</t>
+          <t>46616; 73240</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96074; 131263</t>
+          <t>96203; 132083</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>111271; 145105</t>
+          <t>111229; 144853</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26175; 42294</t>
+          <t>26529; 42243</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94337; 132967</t>
+          <t>94294; 130619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156184; 203166</t>
+          <t>159875; 206860</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203994; 251577</t>
+          <t>206163; 253558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58913; 87509</t>
+          <t>62673; 90240</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201308</t>
+          <t>209414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>210540</t>
+          <t>224960</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>411848</t>
+          <t>434374</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90777; 126675</t>
+          <t>89146; 127038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164752; 211973</t>
+          <t>166003; 210529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121249; 160755</t>
+          <t>121026; 161331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173365; 231232</t>
+          <t>180075; 237199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136651; 175874</t>
+          <t>136632; 178382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206041; 254393</t>
+          <t>203736; 250564</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165951; 211247</t>
+          <t>163669; 212131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>190129; 229957</t>
+          <t>204010; 245652</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>238486; 294119</t>
+          <t>234911; 293378</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381999; 448903</t>
+          <t>383665; 449138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>298512; 358590</t>
+          <t>300037; 359161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>378536; 446845</t>
+          <t>399284; 467897</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87571</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>188801</t>
+          <t>193606</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31146; 55034</t>
+          <t>30288; 54389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60601; 91259</t>
+          <t>61726; 91450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68354; 98608</t>
+          <t>69105; 98091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73036; 102989</t>
+          <t>74337; 104398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48258; 75711</t>
+          <t>48450; 75815</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82933; 117217</t>
+          <t>81826; 116411</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94276; 128327</t>
+          <t>92990; 128333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86235; 114545</t>
+          <t>91034; 118813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83419; 121077</t>
+          <t>84919; 121958</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150001; 195941</t>
+          <t>150838; 195750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170378; 215147</t>
+          <t>169926; 217544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169678; 209803</t>
+          <t>173229; 213477</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67015</t>
+          <t>83005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92557</t>
+          <t>104001</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>159571</t>
+          <t>187007</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48617; 74286</t>
+          <t>48470; 75484</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44849; 74956</t>
+          <t>44381; 73813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94896; 129050</t>
+          <t>95046; 129519</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52243; 84113</t>
+          <t>65705; 105572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68146; 98390</t>
+          <t>70542; 101471</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99730; 136878</t>
+          <t>100656; 136450</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124711; 162448</t>
+          <t>123391; 163540</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58138; 122466</t>
+          <t>87698; 122934</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123285; 165050</t>
+          <t>125429; 166319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>153785; 202315</t>
+          <t>152447; 198483</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>230192; 284227</t>
+          <t>229652; 285513</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114659; 191433</t>
+          <t>164239; 215131</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>115957</t>
+          <t>128581</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11058; 27620</t>
+          <t>10610; 26546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35020; 60213</t>
+          <t>35118; 59628</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70609; 98463</t>
+          <t>71617; 98371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42810; 63687</t>
+          <t>51051; 72817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18269; 37671</t>
+          <t>17925; 37918</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65323; 93160</t>
+          <t>64437; 93813</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95754; 124230</t>
+          <t>94527; 124109</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53347; 71173</t>
+          <t>58361; 79285</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33470; 58778</t>
+          <t>33417; 58742</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105691; 145658</t>
+          <t>106522; 143930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>172695; 213681</t>
+          <t>174629; 214903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>103559; 131425</t>
+          <t>112531; 144170</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>79949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>79971</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>158814</t>
+          <t>159920</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41356; 66825</t>
+          <t>41626; 67224</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64284; 95594</t>
+          <t>65044; 95001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45172; 72493</t>
+          <t>44691; 72921</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69497; 94720</t>
+          <t>67679; 92045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48158; 74539</t>
+          <t>48233; 74859</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89222; 121925</t>
+          <t>91133; 124037</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71110; 100599</t>
+          <t>68590; 100229</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67528; 88775</t>
+          <t>69571; 91856</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96612; 133973</t>
+          <t>92467; 131084</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>160696; 207108</t>
+          <t>163269; 207652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124697; 164937</t>
+          <t>122401; 163440</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>142330; 175677</t>
+          <t>143258; 176021</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147385</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>215135</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>362520</t>
+          <t>432900</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62933; 94224</t>
+          <t>61802; 92403</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>149483; 195095</t>
+          <t>148296; 197679</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169838; 218577</t>
+          <t>168425; 220046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127071; 171380</t>
+          <t>151819; 200875</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67678; 104408</t>
+          <t>68891; 102109</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>203601; 253132</t>
+          <t>201631; 254521</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>215431; 265678</t>
+          <t>212911; 263990</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111420; 292034</t>
+          <t>235311; 283724</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>140299; 186685</t>
+          <t>142120; 187324</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>362482; 434938</t>
+          <t>366897; 431474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>396506; 465584</t>
+          <t>399363; 467065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>241565; 432663</t>
+          <t>400575; 468925</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>415108</t>
+          <t>477950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>471058</t>
+          <t>538482</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>886167</t>
+          <t>1016431</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116228; 158388</t>
+          <t>117422; 159235</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>156095; 207730</t>
+          <t>155958; 206413</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>137966; 181556</t>
+          <t>137994; 182621</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>186647; 571656</t>
+          <t>447283; 506859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>137285; 183661</t>
+          <t>136155; 180786</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>193007; 245289</t>
+          <t>193669; 244576</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>188334; 239761</t>
+          <t>185024; 237613</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>449839; 492062</t>
+          <t>507851; 563014</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>261631; 324510</t>
+          <t>263921; 323809</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>361009; 435679</t>
+          <t>362508; 430151</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>338937; 408873</t>
+          <t>336810; 406702</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>542223; 1054883</t>
+          <t>974090; 1054189</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>510422; 590682</t>
+          <t>508961; 587680</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>808044; 923851</t>
+          <t>808272; 912678</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>878132; 981053</t>
+          <t>879891; 986707</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>843324; 1198696</t>
+          <t>1154652; 1279714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>645355; 734471</t>
+          <t>647402; 744599</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1128096; 1245567</t>
+          <t>1132348; 1251401</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1148481; 1268184</t>
+          <t>1163670; 1273608</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1005768; 1371118</t>
+          <t>1363945; 1468276</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1178787; 1297968</t>
+          <t>1179306; 1298809</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1982308; 2128182</t>
+          <t>1977435; 2130614</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2071546; 2225499</t>
+          <t>2076240; 2232777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2048831; 2530350</t>
+          <t>2555255; 2717022</t>
         </is>
       </c>
     </row>
